--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/Rework run 2/Panel 01/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/Rework run 2/Panel 01/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.34699</v>
+        <v>16.65157</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58718</v>
+        <v>16.51973</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53846</v>
+        <v>16.62897</v>
       </c>
       <c r="F2" t="n">
-        <v>41.40643</v>
+        <v>41.98432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04977</v>
+        <v>0.05002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81964</v>
+        <v>1.73963</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.71501</v>
+        <v>16.64939</v>
       </c>
       <c r="D3" t="n">
-        <v>16.1643</v>
+        <v>16.24216</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60874</v>
+        <v>16.37109</v>
       </c>
       <c r="F3" t="n">
-        <v>41.27086</v>
+        <v>41.49211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05063</v>
+        <v>0.0496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79517</v>
+        <v>1.80842</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65365</v>
+        <v>16.8467</v>
       </c>
       <c r="D4" t="n">
-        <v>16.37144</v>
+        <v>16.56369</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63665</v>
+        <v>16.61851</v>
       </c>
       <c r="F4" t="n">
-        <v>41.52107</v>
+        <v>41.1814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05073</v>
+        <v>0.05012</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79176</v>
+        <v>1.81694</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.71211</v>
+        <v>16.59078</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5683</v>
+        <v>16.21167</v>
       </c>
       <c r="E5" t="n">
-        <v>16.72173</v>
+        <v>16.37695</v>
       </c>
       <c r="F5" t="n">
-        <v>41.50587</v>
+        <v>41.74385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04984</v>
+        <v>0.05156</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81963</v>
+        <v>1.81015</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.78264</v>
+        <v>16.62005</v>
       </c>
       <c r="D6" t="n">
-        <v>16.24536</v>
+        <v>16.15908</v>
       </c>
       <c r="E6" t="n">
-        <v>16.74677</v>
+        <v>16.31392</v>
       </c>
       <c r="F6" t="n">
-        <v>41.56818</v>
+        <v>42.12323</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0497</v>
+        <v>0.05058</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79726</v>
+        <v>1.82505</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.4902</v>
+        <v>16.49959</v>
       </c>
       <c r="D7" t="n">
-        <v>16.16128</v>
+        <v>16.37272</v>
       </c>
       <c r="E7" t="n">
-        <v>16.85981</v>
+        <v>16.49286</v>
       </c>
       <c r="F7" t="n">
-        <v>41.31444</v>
+        <v>42.68925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0494</v>
+        <v>0.04998</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79676</v>
+        <v>1.79216</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.41987</v>
+        <v>16.77236</v>
       </c>
       <c r="D8" t="n">
-        <v>16.71185</v>
+        <v>16.61999</v>
       </c>
       <c r="E8" t="n">
-        <v>16.71919</v>
+        <v>16.65983</v>
       </c>
       <c r="F8" t="n">
-        <v>42.12424</v>
+        <v>41.99739</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04993</v>
+        <v>0.04903</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80352</v>
+        <v>1.78457</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.45773</v>
+        <v>16.81962</v>
       </c>
       <c r="D9" t="n">
-        <v>16.34878</v>
+        <v>16.29776</v>
       </c>
       <c r="E9" t="n">
-        <v>16.45088</v>
+        <v>16.3568</v>
       </c>
       <c r="F9" t="n">
-        <v>42.8194</v>
+        <v>40.91667</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04923</v>
+        <v>0.04943</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79346</v>
+        <v>1.81785</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.52206</v>
+        <v>16.71771</v>
       </c>
       <c r="D10" t="n">
-        <v>16.32117</v>
+        <v>16.51068</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45478</v>
+        <v>16.51792</v>
       </c>
       <c r="F10" t="n">
-        <v>42.81794</v>
+        <v>41.62653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04947</v>
+        <v>0.05069</v>
       </c>
       <c r="H10" t="n">
-        <v>1.78737</v>
+        <v>1.78222</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60529</v>
+        <v>0.60647</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13736</v>
+        <v>1.11981</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60383</v>
+        <v>0.59553</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10589</v>
+        <v>1.12561</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60938</v>
+        <v>0.60195</v>
       </c>
       <c r="D14" t="n">
-        <v>1.08445</v>
+        <v>1.11524</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5858100000000001</v>
+        <v>0.59205</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09827</v>
+        <v>1.10168</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.59944</v>
+        <v>0.62055</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1005</v>
+        <v>1.09554</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59961</v>
+        <v>0.6073</v>
       </c>
       <c r="D17" t="n">
-        <v>1.08169</v>
+        <v>1.10312</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60449</v>
+        <v>0.61212</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08652</v>
+        <v>1.09472</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6113499999999999</v>
+        <v>0.57711</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09916</v>
+        <v>1.08955</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60638</v>
+        <v>0.58561</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09525</v>
+        <v>1.11851</v>
       </c>
     </row>
   </sheetData>
